--- a/results/Int All Data -0.9/Rando_2_permute.xlsx
+++ b/results/Int All Data -0.9/Rando_2_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7225504604450155</v>
+        <v>0.737731007952189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7249553169355796</v>
+        <v>0.7361986930203657</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7249202337482807</v>
+        <v>0.7392984060713114</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7249202337482807</v>
+        <v>0.7406553050666406</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7249202337482807</v>
+        <v>0.7411068483777954</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7263801132436414</v>
+        <v>0.7393334892586103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7263801132436414</v>
+        <v>0.7469554426066982</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7288856811723718</v>
+        <v>0.7469905257939971</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7271100529913217</v>
+        <v>0.7526682422101361</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7270749698040229</v>
+        <v>0.7526682422101361</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7263427609944775</v>
+        <v>0.7553865783245247</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7292014298580614</v>
+        <v>0.765661239536134</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7308039111644825</v>
+        <v>0.7669853244060294</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7315689340994618</v>
+        <v>0.7639206945423827</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7312203712883385</v>
+        <v>0.7724898939475393</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7323316879725758</v>
+        <v>0.7810240101653971</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7319480419741536</v>
+        <v>0.7836767180289184</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7319106897249896</v>
+        <v>0.7837118012162172</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7321890861615152</v>
+        <v>0.7837118012162172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.730032081043908</v>
+        <v>0.7840252808400416</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7289513094232394</v>
+        <v>0.7831878224685997</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7294028527343941</v>
+        <v>0.7828743428447752</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7289467712995092</v>
+        <v>0.7840230117781766</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7307789514839664</v>
+        <v>0.7855904098972988</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7132546376133658</v>
+        <v>0.7794237979208412</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7152362267944788</v>
+        <v>0.7842640559655382</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7086531546941653</v>
+        <v>0.7842640559655382</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7075372998861978</v>
+        <v>0.7823458259734275</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7061781318290035</v>
+        <v>0.7837049940306219</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7055138203321907</v>
+        <v>0.7857590186481976</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7072215512005082</v>
+        <v>0.7863508947085477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7067745460130838</v>
+        <v>0.7869427707688978</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.707331338886135</v>
+        <v>0.785307475337043</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7056983125161452</v>
+        <v>0.785307475337043</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7260043216901368</v>
+        <v>0.785307475337043</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7242196172616263</v>
+        <v>0.783117656094002</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7320939601064016</v>
+        <v>0.7794634192318701</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7122621848622155</v>
+        <v>0.7846567782114207</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7047737570777275</v>
+        <v>0.7797440847302609</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7015314422157215</v>
+        <v>0.7796037519810656</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7006589006569807</v>
+        <v>0.7952890784816136</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7009372970935063</v>
+        <v>0.7930245547402448</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7008343165934749</v>
+        <v>0.7930245547402448</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7013911094665262</v>
+        <v>0.7909331778735051</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7021561324015053</v>
+        <v>0.7885305904448059</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6908685968819599</v>
+        <v>0.7913496379973609</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6904147845089401</v>
+        <v>0.798629835719921</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6925740586884124</v>
+        <v>0.7937567635497902</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6898229084485901</v>
+        <v>0.8064713644392625</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6985697928521061</v>
+        <v>0.8046866600107518</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7040347410825869</v>
+        <v>0.8049299732599786</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.69368991349638</v>
+        <v>0.7936141617387298</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6989489007267979</v>
+        <v>0.7936141617387298</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6646211364858166</v>
+        <v>0.7944516201101717</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6646211364858166</v>
+        <v>0.7784313451696909</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6646211364858166</v>
+        <v>0.7737619649377578</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6632291543031885</v>
+        <v>0.7812458545985157</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6736769623894269</v>
+        <v>0.7812458545985157</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6733634827656024</v>
+        <v>0.7812809377858145</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6804309123025043</v>
+        <v>0.7877893053878001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6779230753119088</v>
+        <v>0.785347096648072</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6808360271170347</v>
+        <v>0.7700895755807053</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6555403509016903</v>
+        <v>0.7712687895776753</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.645132164126481</v>
+        <v>0.7698417242077483</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.64575912337413</v>
+        <v>0.7711329949522101</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6492334061760373</v>
+        <v>0.7787617554858934</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6495468857998618</v>
+        <v>0.7789371714223876</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6511821812317166</v>
+        <v>0.7809583819145296</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6501715759856456</v>
+        <v>0.7510725680893102</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6302005152515866</v>
+        <v>0.7461949577954493</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6491824395556828</v>
+        <v>0.7453903135494411</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6475097918746641</v>
+        <v>0.7461576055462854</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6211050680369473</v>
+        <v>0.7323667711598746</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6213789263497427</v>
+        <v>0.7320328699792642</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6244412871515245</v>
+        <v>0.7338039600365842</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5890746416627686</v>
+        <v>0.7554453993897969</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5925229175248375</v>
+        <v>0.7531717994009677</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5945090448296807</v>
+        <v>0.7592026167519601</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5946142943915772</v>
+        <v>0.7595297107469752</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5960062765742054</v>
+        <v>0.766042616472691</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6007130090553022</v>
+        <v>0.7669807862822993</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6007130090553022</v>
+        <v>0.7709088814572265</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6056585166618957</v>
+        <v>0.7673157347222319</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6089313765874707</v>
+        <v>0.6983467266164447</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6142582611306212</v>
+        <v>0.698695289427568</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6117855073273244</v>
+        <v>0.6915508863304731</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6233887915325593</v>
+        <v>0.6228433439688336</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6299741326947379</v>
+        <v>0.622775446656101</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.630186900880396</v>
+        <v>0.6284882462595388</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6246121649642884</v>
+        <v>0.6198816946052181</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6094225412096543</v>
+        <v>0.6191121335465087</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6106062933303544</v>
+        <v>0.6268857649531177</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6046128282285259</v>
+        <v>0.6256318464578199</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5537849697342055</v>
+        <v>0.6187658397972506</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5537849697342055</v>
+        <v>0.6085918900238076</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5395097779112064</v>
+        <v>0.608313493587282</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.535921169299942</v>
+        <v>0.6033861384756093</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5406233636573088</v>
+        <v>0.6055103294677828</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5659823990616557</v>
+        <v>0.6055103294677828</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5774453505176952</v>
+        <v>0.5971425529389587</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5768183912700463</v>
+        <v>0.5850594494208656</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5831276050575643</v>
+        <v>0.5836629291145073</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.568941779363406</v>
+        <v>0.5616333056391424</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5801942316956524</v>
+        <v>0.5448038483289233</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5804375449448793</v>
+        <v>0.5386372363524656</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5805077113194769</v>
+        <v>0.5383237567286412</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5412265850269844</v>
+        <v>0.5371071904825073</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5302547981931286</v>
+        <v>0.5344941039300152</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5314340121900984</v>
+        <v>0.5356755869888502</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5375655409792572</v>
+        <v>0.5326743163142057</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5299718636328727</v>
+        <v>0.5320473570665568</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5181275352402762</v>
+        <v>0.5292260404521367</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.514085114255992</v>
+        <v>0.5292260404521367</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5137342823830037</v>
+        <v>0.5298179165124868</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5083326933415252</v>
+        <v>0.5297477501378891</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5083326933415252</v>
+        <v>0.5297477501378891</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5074250685954856</v>
+        <v>0.529955980199817</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5074250685954856</v>
+        <v>0.5219503808533069</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5057569590381971</v>
+        <v>0.5174213333705692</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5122042365130454</v>
+        <v>0.5157136025022516</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5122042365130454</v>
+        <v>0.5195104411754439</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5045075786666294</v>
+        <v>0.5124384735148118</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.504194099042805</v>
+        <v>0.5113927850814419</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5105666720193254</v>
+        <v>0.5112875355195453</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5097665658970474</v>
+        <v>0.5109740558957209</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5062481236603807</v>
+        <v>0.5115331178306373</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5051345379142783</v>
+        <v>0.5118884878273559</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5069101660953285</v>
+        <v>0.5118884878273559</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5073288952810495</v>
+        <v>0.501414672801279</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5026595150491164</v>
+        <v>0.4760149688265808</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4995971542473348</v>
+        <v>0.5014474869267128</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4965279862599577</v>
+        <v>0.4934441566420677</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4292284840572222</v>
+        <v>0.4934441566420677</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4295419636810467</v>
+        <v>0.4934441566420677</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4364294391577243</v>
+        <v>0.5095606048969846</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4501387618602118</v>
+        <v>0.4902596155860114</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4723052272203643</v>
+        <v>0.491719495081372</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4856309039244298</v>
+        <v>0.4825720339870559</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4907450202819222</v>
+        <v>0.5005070480552394</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4932155050233539</v>
+        <v>0.4910461073370989</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4997216035634744</v>
+        <v>0.4910461073370989</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4997216035634744</v>
+        <v>0.4891652295941522</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.4755260732662622</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4997216035634744</v>
+        <v>0.4766045758250658</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4997216035634744</v>
+        <v>0.4766045758250658</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4986431010046707</v>
+        <v>0.4782025190077567</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4816790708715292</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4989565806284952</v>
+        <v>0.4832464689906515</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4997566867507732</v>
+        <v>0.4913550488371931</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5000350831872988</v>
+        <v>0.4905198595276162</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5000350831872988</v>
+        <v>0.4905198595276162</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5000350831872988</v>
+        <v>0.4832487380525166</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5000350831872988</v>
+        <v>0.4972533878839078</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4972533878839078</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4971130551347125</v>
       </c>
     </row>
   </sheetData>
